--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -979,7 +979,7 @@
         <v>44.9</v>
       </c>
       <c r="D13">
-        <v>47.73119999999992</v>
+        <v>47.73119999999993</v>
       </c>
       <c r="E13">
         <v>51.7</v>
@@ -997,19 +997,19 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="J13">
-        <v>-1.600400000000046</v>
+        <v>-1.600400000000041</v>
       </c>
       <c r="K13">
-        <v>5.199599999999954</v>
+        <v>5.199599999999959</v>
       </c>
       <c r="L13">
         <v>-7.039337474120083</v>
       </c>
       <c r="M13">
-        <v>-1.648829417655423</v>
+        <v>-1.648829417655417</v>
       </c>
       <c r="N13">
-        <v>5.39050805646466</v>
+        <v>5.390508056464666</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1111,7 +1111,7 @@
         <v>47.3</v>
       </c>
       <c r="D16">
-        <v>47.59039999999993</v>
+        <v>47.59039999999992</v>
       </c>
       <c r="E16">
         <v>50</v>
@@ -1123,25 +1123,25 @@
         <v>2.700000000000002</v>
       </c>
       <c r="H16">
-        <v>3.104800000000163</v>
+        <v>3.104800000000174</v>
       </c>
       <c r="I16">
         <v>-2.700000000000002</v>
       </c>
       <c r="J16">
-        <v>-1.714399999999972</v>
+        <v>-1.714399999999977</v>
       </c>
       <c r="K16">
-        <v>0.9856000000000309</v>
+        <v>0.9856000000000253</v>
       </c>
       <c r="L16">
         <v>-2.774922918807813</v>
       </c>
       <c r="M16">
-        <v>-1.769334291069087</v>
+        <v>-1.769334291069093</v>
       </c>
       <c r="N16">
-        <v>1.005588627738726</v>
+        <v>1.00558862773872</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1607,25 +1607,25 @@
         <v>3.399999999999998</v>
       </c>
       <c r="H27">
-        <v>2.622800000000114</v>
+        <v>2.622800000000103</v>
       </c>
       <c r="I27">
         <v>8.000000000000002</v>
       </c>
       <c r="J27">
-        <v>0.3420000000001255</v>
+        <v>0.3420000000001311</v>
       </c>
       <c r="K27">
-        <v>7.657999999999881</v>
+        <v>7.657999999999871</v>
       </c>
       <c r="L27">
         <v>8.281573498964805</v>
       </c>
       <c r="M27">
-        <v>0.3512115772481915</v>
+        <v>0.3512115772481972</v>
       </c>
       <c r="N27">
-        <v>7.930361921716614</v>
+        <v>7.930361921716608</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1689,31 +1689,31 @@
         <v>51.2</v>
       </c>
       <c r="F29">
-        <v>48.7575999999999</v>
+        <v>48.75759999999989</v>
       </c>
       <c r="G29">
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.94000000000017</v>
+        <v>2.940000000000176</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.4551999999999612</v>
+        <v>-0.4551999999999556</v>
       </c>
       <c r="K29">
-        <v>5.244800000000039</v>
+        <v>5.244800000000044</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.4689882546877828</v>
+        <v>-0.4689882546877771</v>
       </c>
       <c r="N29">
-        <v>5.425530876646239</v>
+        <v>5.425530876646245</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1739,25 +1739,25 @@
         <v>1.799999999999996</v>
       </c>
       <c r="H30">
-        <v>3.208400000000172</v>
+        <v>3.208400000000167</v>
       </c>
       <c r="I30">
         <v>8.600000000000001</v>
       </c>
       <c r="J30">
-        <v>-0.5244000000000526</v>
+        <v>-0.5244000000000582</v>
       </c>
       <c r="K30">
-        <v>9.124400000000049</v>
+        <v>9.12440000000006</v>
       </c>
       <c r="L30">
         <v>8.757637474541752</v>
       </c>
       <c r="M30">
-        <v>-0.5417825513784807</v>
+        <v>-0.5417825513784864</v>
       </c>
       <c r="N30">
-        <v>9.299420025920233</v>
+        <v>9.299420025920238</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2041,13 +2041,13 @@
         <v>44.3</v>
       </c>
       <c r="F37">
-        <v>47.61983181443601</v>
+        <v>47.619831814436</v>
       </c>
       <c r="G37">
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.423429944016342</v>
+        <v>2.423429944016359</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
@@ -2062,10 +2062,10 @@
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.394946272215611</v>
+        <v>2.394946272215612</v>
       </c>
       <c r="N37">
-        <v>5.886627226749194</v>
+        <v>5.886627226749193</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2123,19 +2123,19 @@
         <v>45.5</v>
       </c>
       <c r="D39">
-        <v>48.10567147557039</v>
+        <v>48.1056714755704</v>
       </c>
       <c r="E39">
         <v>51.2</v>
       </c>
       <c r="F39">
-        <v>48.95113339758256</v>
+        <v>48.95113339758257</v>
       </c>
       <c r="G39">
         <v>3.299999999999992</v>
       </c>
       <c r="H39">
-        <v>2.943195126847054</v>
+        <v>2.943195126847031</v>
       </c>
       <c r="I39">
         <v>-5.699999999999999</v>
@@ -2150,10 +2150,10 @@
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>-0.8711000976357447</v>
+        <v>-0.8711000976357445</v>
       </c>
       <c r="N39">
-        <v>5.023419033698277</v>
+        <v>5.023419033698278</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2167,37 +2167,37 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.3763767479223</v>
+        <v>48.37637674792231</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.43105651824636</v>
+        <v>48.43105651824637</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.192566733831337</v>
+        <v>3.192566733831326</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
       </c>
       <c r="J40">
-        <v>-0.05467977032406202</v>
+        <v>-0.05467977032406757</v>
       </c>
       <c r="K40">
-        <v>8.654679770324064</v>
+        <v>8.654679770324075</v>
       </c>
       <c r="L40">
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>-0.05648302870888219</v>
+        <v>-0.05648302870888792</v>
       </c>
       <c r="N40">
-        <v>8.814120503250635</v>
+        <v>8.81412050325064</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2229,19 +2229,19 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="J41">
-        <v>-1.048624949950228</v>
+        <v>-1.048624949950233</v>
       </c>
       <c r="K41">
-        <v>1.651375050049775</v>
+        <v>1.651375050049769</v>
       </c>
       <c r="L41">
         <v>-2.774922918807813</v>
       </c>
       <c r="M41">
-        <v>-1.081718299630196</v>
+        <v>-1.081718299630202</v>
       </c>
       <c r="N41">
-        <v>1.693204619177617</v>
+        <v>1.693204619177612</v>
       </c>
     </row>
   </sheetData>
